--- a/backend/data/temp/Ventas.xlsx
+++ b/backend/data/temp/Ventas.xlsx
@@ -397,65 +397,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AV8"/>
+  <dimension ref="A1:AV11"/>
   <sheetData>
     <row r="4">
       <c r="A4" t="str">
-        <v>00000049</v>
+        <v>00000010</v>
       </c>
       <c r="B4" t="str">
-        <v>25 de febrero de 2026 10:25 hs.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Paquete de 3 productos</v>
+        <v>26 de febrero de 2026 13:27 hs.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v>57315</v>
-      </c>
-      <c r="H4" t="str">
-        <v>-1000</v>
-      </c>
-      <c r="J4" t="str">
-        <v>-838</v>
-      </c>
-      <c r="K4" t="str">
-        <v>-139</v>
+        <v>87878</v>
       </c>
       <c r="L4" t="str">
-        <v>58315</v>
+        <v>87878</v>
+      </c>
+      <c r="N4" t="str">
+        <v>47896312584654</v>
+      </c>
+      <c r="R4" t="str">
+        <v>29293</v>
+      </c>
+      <c r="S4" t="str">
+        <v>V</v>
       </c>
       <c r="T4" t="str">
         <v/>
       </c>
       <c r="U4" t="str">
-        <v>Rodri Depaul</v>
+        <v>Jorgelina Iglesias</v>
       </c>
       <c r="V4" t="str">
-        <v>DNI 23233323</v>
+        <v>DNI 33234232</v>
       </c>
       <c r="W4" t="str">
-        <v>CATAMARCA 955, Córdoba - C.P.: 5004, Cordoba</v>
+        <v>AVENIDA SAN MARTIN 323, VILLA CARLOS PAZ - C.P.: 5152, Cordoba</v>
       </c>
       <c r="X4" t="str">
         <v>CF</v>
       </c>
       <c r="Y4" t="str">
-        <v>Rodri Depaul</v>
+        <v>Jorgelina Iglesias</v>
       </c>
       <c r="Z4" t="str">
-        <v>23233323</v>
+        <v>33234232</v>
       </c>
       <c r="AA4" t="str">
-        <v>CATAMARCA 955, Córdoba - C.P.: 5004, Cordoba</v>
+        <v>AVENIDA SAN MARTIN 323, VILLA CARLOS PAZ - C.P.: 5152, Cordoba</v>
       </c>
       <c r="AB4" t="str">
-        <v>Córdoba</v>
+        <v>VILLA CARLOS PAZ</v>
       </c>
       <c r="AC4" t="str">
         <v>Cordoba</v>
       </c>
       <c r="AD4" t="str">
-        <v>5004</v>
+        <v>5152</v>
       </c>
       <c r="AE4" t="str">
         <v>ARGENTINA</v>
@@ -467,16 +467,16 @@
         <v>TRANS</v>
       </c>
       <c r="AN4" t="str">
-        <v>57315</v>
+        <v>106332</v>
       </c>
       <c r="AO4" t="str">
-        <v>58315</v>
+        <v>107332</v>
       </c>
       <c r="AP4" t="str">
         <v>0</v>
       </c>
       <c r="AS4" t="str">
-        <v>Rodri Depaul</v>
+        <v>Jorgelina Iglesias</v>
       </c>
       <c r="AT4" t="str">
         <v>360000102000579</v>
@@ -490,85 +490,289 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>00000049</v>
+        <v>00000050</v>
       </c>
       <c r="B5" t="str">
-        <v>25 de febrero de 2026 10:25 hs.</v>
-      </c>
-      <c r="F5" t="str">
-        <v>1</v>
-      </c>
-      <c r="N5" t="str">
-        <v>6928073600597</v>
-      </c>
-      <c r="O5" t="str">
-        <v>633500</v>
-      </c>
-      <c r="P5" t="str">
+        <v>26 de febrero de 2026 10:51 hs.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Paquete de 4 productos</v>
+      </c>
+      <c r="G5" t="str">
+        <v>230698</v>
+      </c>
+      <c r="H5" t="str">
+        <v>-1000</v>
+      </c>
+      <c r="J5" t="str">
+        <v>-838</v>
+      </c>
+      <c r="K5" t="str">
+        <v>-139</v>
+      </c>
+      <c r="L5" t="str">
+        <v>231698</v>
+      </c>
+      <c r="T5" t="str">
         <v/>
       </c>
-      <c r="Q5" t="str">
-        <v>PISTOLA DE AIRE PARA SOPLETEAR 16MM (CONECTOR EUROPEO)- ABG031</v>
-      </c>
-      <c r="R5" t="str">
-        <v>17728</v>
+      <c r="U5" t="str">
+        <v>Ignacio Ferreyra</v>
+      </c>
+      <c r="V5" t="str">
+        <v>DNI 2323323</v>
+      </c>
+      <c r="W5" t="str">
+        <v>CALLE 3 323, General Pico - C.P.: 6360, La Pampa</v>
+      </c>
+      <c r="X5" t="str">
+        <v>CF</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Ignacio Ferreyra</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>2323323</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>CALLE 3 323, General Pico - C.P.: 6360, La Pampa</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>General Pico</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>La Pampa</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>6360</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>ARGENTINA</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>ANDREANI</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>TRANS</v>
+      </c>
+      <c r="AN5" t="str">
+        <v>230698</v>
+      </c>
+      <c r="AO5" t="str">
+        <v>231698</v>
+      </c>
+      <c r="AP5" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="str">
+        <v>Ignacio Ferreyra</v>
+      </c>
+      <c r="AT5" t="str">
+        <v>360000102000579</v>
+      </c>
+      <c r="AU5" t="str">
+        <v>CORDOBA - RECANALIZACION</v>
+      </c>
+      <c r="AV5" t="str">
+        <v>PROCESAMIENTO CIT POSTAL</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>00000049</v>
+        <v>00000050</v>
       </c>
       <c r="B6" t="str">
-        <v>25 de febrero de 2026 10:25 hs.</v>
+        <v>26 de febrero de 2026 10:51 hs.</v>
       </c>
       <c r="F6" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="str">
-        <v>6941640180032</v>
+        <v>4589615833547</v>
       </c>
       <c r="O6" t="str">
-        <v>633470</v>
+        <v>633501</v>
       </c>
       <c r="P6" t="str">
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>PISTOLA ENGRASADORA A BATERIA 20V -GGLI2010  INGCO</v>
+        <v>JGO 31 PUNTAS DE IMPACTO AKDL11306 INGCO</v>
       </c>
       <c r="R6" t="str">
-        <v>12100</v>
+        <v>36784</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>00000049</v>
+        <v>00000050</v>
       </c>
       <c r="B7" t="str">
-        <v>25 de febrero de 2026 10:25 hs.</v>
+        <v>26 de febrero de 2026 10:51 hs.</v>
       </c>
       <c r="F7" t="str">
         <v>1</v>
       </c>
       <c r="N7" t="str">
-        <v>6973138727009</v>
+        <v>6942141804571</v>
       </c>
       <c r="O7" t="str">
-        <v>633498</v>
+        <v>633499</v>
       </c>
       <c r="P7" t="str">
         <v/>
       </c>
       <c r="Q7" t="str">
+        <v>SIERRA WIDIA 2PCS 165MM 24D TSB1653 INGCO</v>
+      </c>
+      <c r="R7" t="str">
+        <v>28827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>00000050</v>
+      </c>
+      <c r="B8" t="str">
+        <v>26 de febrero de 2026 10:51 hs.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2</v>
+      </c>
+      <c r="N8" t="str">
+        <v>6973138727009</v>
+      </c>
+      <c r="O8" t="str">
+        <v>633498</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
         <v>DISCO DESBASTE 230X6MM MGD602301 INGCO</v>
       </c>
-      <c r="R7" t="str">
+      <c r="R8" t="str">
         <v>17540</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>00000050</v>
+      </c>
+      <c r="B9" t="str">
+        <v>26 de febrero de 2026 10:51 hs.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>3</v>
+      </c>
+      <c r="N9" t="str">
+        <v>6928073600597</v>
+      </c>
+      <c r="O9" t="str">
+        <v>633500</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>PISTOLA DE AIRE PARA SOPLETEAR 16MM (CONECTOR EUROPEO)- ABG031</v>
+      </c>
+      <c r="R9" t="str">
+        <v>17728</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>00000051</v>
+      </c>
+      <c r="B10" t="str">
+        <v>26 de febrero de 2026 10:53 hs.</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>184050</v>
+      </c>
+      <c r="L10" t="str">
+        <v>184050</v>
+      </c>
+      <c r="N10" t="str">
+        <v>416461131361641645</v>
+      </c>
+      <c r="R10" t="str">
+        <v>184050</v>
+      </c>
+      <c r="S10" t="str">
+        <v>V</v>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v>Valeria Massamoni</v>
+      </c>
+      <c r="V10" t="str">
+        <v>DNI 33232117</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Ituzaingo 300, Córdoba - C.P.: 5000, Cordoba</v>
+      </c>
+      <c r="X10" t="str">
+        <v>CF</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Valeria Massamoni</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>33232117</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>Ituzaingo 300, Córdoba - C.P.: 5000, Cordoba</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>Córdoba</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>Cordoba</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>5000</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>ARGENTINA</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>ANDREANI</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>TRANS</v>
+      </c>
+      <c r="AN10" t="str">
+        <v>222700</v>
+      </c>
+      <c r="AO10" t="str">
+        <v>223700</v>
+      </c>
+      <c r="AP10" t="str">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="str">
+        <v>Valeria Massamoni</v>
+      </c>
+      <c r="AT10" t="str">
+        <v>360000102000579</v>
+      </c>
+      <c r="AU10" t="str">
+        <v>CORDOBA - RECANALIZACION</v>
+      </c>
+      <c r="AV10" t="str">
+        <v>PROCESAMIENTO CIT POSTAL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AV8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AV11"/>
   </ignoredErrors>
 </worksheet>
 </file>